--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126548938</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98336</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väg ned mot Ljungstorp/Smedsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531402</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6458340</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Wallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Wallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>126548938</v>
       </c>
       <c r="B4" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127784008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ljungstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531557</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6458467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127784008</v>
       </c>
       <c r="B5" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101997247</v>
+        <v>103986637</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>83330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>4202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Geoglossum umbratile</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ljungstorp, 350 m ONO, Skeda udde, Ög</t>
+          <t>Ljungstorp, 250 m Ö, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531492.4239714351</v>
+        <v>531431</v>
       </c>
       <c r="R2" t="n">
-        <v>6458403.16687279</v>
+        <v>6458382</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>många ex på vägkanten, där man kan ställa bilen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,38 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skogsväg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Nyström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Nyström, Karin Nyström</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103986637</v>
+        <v>126548938</v>
       </c>
       <c r="B3" t="n">
-        <v>76579</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,40 +792,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4202</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljungstorp, 250 m Ö, Ög</t>
+          <t>Väg ned mot Ljungstorp/Smedsbo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531431.4505192675</v>
+        <v>531402</v>
       </c>
       <c r="R3" t="n">
-        <v>6458382.163861016</v>
+        <v>6458340</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,27 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>många ex på vägkanten, där man kan ställa bilen</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Thomas Wallin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Thomas Wallin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126548938</v>
+        <v>127784008</v>
       </c>
       <c r="B4" t="n">
-        <v>98411</v>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,45 +898,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väg ned mot Ljungstorp/Smedsbo, Ög</t>
+          <t>Ljungstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531402</v>
+        <v>531557</v>
       </c>
       <c r="R4" t="n">
-        <v>6458340</v>
+        <v>6458467</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,22 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Wallin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Wallin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127784008</v>
+        <v>101997247</v>
       </c>
       <c r="B5" t="n">
-        <v>105609</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,41 +1000,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljungstorp, Ög</t>
+          <t>Ljungstorp, 350 m ONO, Skeda udde, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531557</v>
+        <v>531492</v>
       </c>
       <c r="R5" t="n">
-        <v>6458467</v>
+        <v>6458403</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,19 +1072,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Bengt Nyström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Bengt Nyström, Karin Nyström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 9192-2025 artfynd.xlsx
+++ b/artfynd/A 9192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986637</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126548938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127784008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101997247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>